--- a/artfynd/A 30121-2023 artfynd.xlsx
+++ b/artfynd/A 30121-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30121-2023 artfynd.xlsx
+++ b/artfynd/A 30121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80461269</v>
+        <v>81008937</v>
       </c>
       <c r="B2" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,35 +705,34 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>1K+</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrefors, O Sågen, Sm</t>
+          <t>Orrefors, Dagvattendike Ö sågverket, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545701.1932652318</v>
+        <v>545721</v>
       </c>
       <c r="R2" t="n">
-        <v>6299401.798432423</v>
+        <v>6299254</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +759,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -802,6 +785,121 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>80461269</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Orrefors, O Sågen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545701</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6299402</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hälleberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Olof Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olof Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30121-2023 artfynd.xlsx
+++ b/artfynd/A 30121-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81008937</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80461269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>